--- a/datos_prueba_ficticios.xlsx
+++ b/datos_prueba_ficticios.xlsx
@@ -71,7 +71,7 @@
     <t>MARCA</t>
   </si>
   <si>
-    <t>CÃ³digo barra principal</t>
+    <t>Código barra principal</t>
   </si>
   <si>
     <t>Costo prom. unit. (ins)</t>
